--- a/Thesis/developer_states_exported.xlsx
+++ b/Thesis/developer_states_exported.xlsx
@@ -1488,7 +1488,7 @@
         <v>329</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D2">
         <v>120</v>
@@ -1541,7 +1541,7 @@
         <v>330</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D3">
         <v>109.3</v>
@@ -1597,7 +1597,7 @@
         <v>331</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D4">
         <v>440</v>
@@ -1653,7 +1653,7 @@
         <v>331</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D5">
         <v>440</v>
@@ -1709,7 +1709,7 @@
         <v>332</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D6">
         <v>60</v>
@@ -1762,7 +1762,7 @@
         <v>332</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -1815,7 +1815,7 @@
         <v>333</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D8">
         <v>8.4</v>
@@ -1871,7 +1871,7 @@
         <v>333</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D9">
         <v>18.15</v>
@@ -1927,7 +1927,7 @@
         <v>333</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D10">
         <v>294.7</v>
@@ -1983,7 +1983,7 @@
         <v>333</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D11">
         <v>150</v>
@@ -2039,7 +2039,7 @@
         <v>332</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D12">
         <v>30</v>
@@ -2092,7 +2092,7 @@
         <v>330</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D13">
         <v>299</v>
@@ -2148,7 +2148,7 @@
         <v>332</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D14">
         <v>62.4</v>
@@ -2201,7 +2201,7 @@
         <v>332</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D15">
         <v>43.2</v>
@@ -2254,7 +2254,7 @@
         <v>332</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D16">
         <v>200</v>
@@ -2307,7 +2307,7 @@
         <v>332</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D17">
         <v>500</v>
@@ -2360,7 +2360,7 @@
         <v>330</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D18">
         <v>95.09999999999999</v>
@@ -2416,7 +2416,7 @@
         <v>330</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D19">
         <v>300</v>
@@ -2472,7 +2472,7 @@
         <v>330</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D20">
         <v>300</v>
@@ -2528,7 +2528,7 @@
         <v>330</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D21">
         <v>118.6</v>
@@ -2584,7 +2584,7 @@
         <v>330</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D22">
         <v>200</v>
@@ -2640,7 +2640,7 @@
         <v>330</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D23">
         <v>90</v>
@@ -2696,7 +2696,7 @@
         <v>330</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D24">
         <v>144</v>
@@ -2752,7 +2752,7 @@
         <v>330</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -2808,7 +2808,7 @@
         <v>332</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D26">
         <v>20</v>
@@ -2861,7 +2861,7 @@
         <v>332</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D27">
         <v>42.2</v>
@@ -2914,7 +2914,7 @@
         <v>329</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D28">
         <v>20</v>
@@ -2967,7 +2967,7 @@
         <v>330</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D29">
         <v>150</v>
@@ -3023,7 +3023,7 @@
         <v>330</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D30">
         <v>100</v>
@@ -3079,7 +3079,7 @@
         <v>333</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D31">
         <v>79.5</v>
@@ -3135,7 +3135,7 @@
         <v>330</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D32">
         <v>150</v>
@@ -3191,7 +3191,7 @@
         <v>330</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D33">
         <v>150</v>
@@ -3247,7 +3247,7 @@
         <v>332</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D34">
         <v>50</v>
@@ -3300,7 +3300,7 @@
         <v>332</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D35">
         <v>50</v>
@@ -3353,7 +3353,7 @@
         <v>330</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D36">
         <v>300</v>
@@ -3409,7 +3409,7 @@
         <v>332</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D37">
         <v>80</v>
@@ -3462,7 +3462,7 @@
         <v>333</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D38">
         <v>199</v>
@@ -3518,7 +3518,7 @@
         <v>330</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D39">
         <v>100</v>
@@ -3574,7 +3574,7 @@
         <v>330</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D40">
         <v>200</v>
@@ -3630,7 +3630,7 @@
         <v>330</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D41">
         <v>300</v>
@@ -3686,7 +3686,7 @@
         <v>330</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D42">
         <v>200</v>
@@ -3742,7 +3742,7 @@
         <v>332</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D43">
         <v>20</v>
@@ -3795,7 +3795,7 @@
         <v>333</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D44">
         <v>175</v>
@@ -3851,7 +3851,7 @@
         <v>332</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D45">
         <v>11</v>
@@ -3904,7 +3904,7 @@
         <v>332</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D46">
         <v>11</v>
@@ -3957,7 +3957,7 @@
         <v>330</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D47">
         <v>200</v>
@@ -4013,7 +4013,7 @@
         <v>333</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D48">
         <v>255</v>
@@ -4069,7 +4069,7 @@
         <v>333</v>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D49">
         <v>180</v>
@@ -4125,7 +4125,7 @@
         <v>332</v>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D50">
         <v>52.2</v>
@@ -4178,7 +4178,7 @@
         <v>330</v>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D51">
         <v>100</v>
@@ -4234,7 +4234,7 @@
         <v>330</v>
       </c>
       <c r="C52">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D52">
         <v>300</v>
@@ -4290,7 +4290,7 @@
         <v>330</v>
       </c>
       <c r="C53">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D53">
         <v>150</v>
@@ -4346,7 +4346,7 @@
         <v>333</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D54">
         <v>150</v>
@@ -4402,7 +4402,7 @@
         <v>332</v>
       </c>
       <c r="C55">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D55">
         <v>50</v>
@@ -4455,7 +4455,7 @@
         <v>330</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D56">
         <v>300</v>
@@ -4511,7 +4511,7 @@
         <v>333</v>
       </c>
       <c r="C57">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D57">
         <v>300</v>
@@ -4567,7 +4567,7 @@
         <v>332</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D58">
         <v>150</v>
@@ -4620,7 +4620,7 @@
         <v>332</v>
       </c>
       <c r="C59">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D59">
         <v>150</v>
@@ -4673,7 +4673,7 @@
         <v>332</v>
       </c>
       <c r="C60">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D60">
         <v>100</v>
@@ -4726,7 +4726,7 @@
         <v>333</v>
       </c>
       <c r="C61">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D61">
         <v>150</v>
@@ -4782,7 +4782,7 @@
         <v>333</v>
       </c>
       <c r="C62">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D62">
         <v>299.97</v>
@@ -4838,7 +4838,7 @@
         <v>330</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D63">
         <v>260</v>
@@ -4894,7 +4894,7 @@
         <v>333</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D64">
         <v>212</v>
@@ -4950,7 +4950,7 @@
         <v>330</v>
       </c>
       <c r="C65">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D65">
         <v>200</v>
@@ -5006,7 +5006,7 @@
         <v>330</v>
       </c>
       <c r="C66">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D66">
         <v>255</v>
@@ -5062,7 +5062,7 @@
         <v>333</v>
       </c>
       <c r="C67">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D67">
         <v>190.89</v>
@@ -5118,7 +5118,7 @@
         <v>334</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D68">
         <v>11</v>
@@ -5174,7 +5174,7 @@
         <v>330</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D69">
         <v>300</v>
@@ -5230,7 +5230,7 @@
         <v>330</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D70">
         <v>200</v>
@@ -5286,7 +5286,7 @@
         <v>330</v>
       </c>
       <c r="C71">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D71">
         <v>346</v>
@@ -5342,7 +5342,7 @@
         <v>330</v>
       </c>
       <c r="C72">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D72">
         <v>100</v>
@@ -5398,7 +5398,7 @@
         <v>333</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D73">
         <v>100</v>
@@ -5454,7 +5454,7 @@
         <v>330</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D74">
         <v>100</v>
@@ -5510,7 +5510,7 @@
         <v>330</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D75">
         <v>150</v>
@@ -5566,7 +5566,7 @@
         <v>333</v>
       </c>
       <c r="C76">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D76">
         <v>200</v>
@@ -5622,7 +5622,7 @@
         <v>333</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D77">
         <v>200</v>
@@ -5678,7 +5678,7 @@
         <v>332</v>
       </c>
       <c r="C78">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D78">
         <v>200</v>
@@ -5731,7 +5731,7 @@
         <v>330</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D79">
         <v>100</v>
@@ -5787,7 +5787,7 @@
         <v>330</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D80">
         <v>140</v>
@@ -5843,7 +5843,7 @@
         <v>330</v>
       </c>
       <c r="C81">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D81">
         <v>100</v>
@@ -5899,7 +5899,7 @@
         <v>330</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D82">
         <v>210</v>
@@ -5955,7 +5955,7 @@
         <v>330</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D83">
         <v>450</v>
@@ -6011,7 +6011,7 @@
         <v>330</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D84">
         <v>180</v>
@@ -6067,7 +6067,7 @@
         <v>332</v>
       </c>
       <c r="C85">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D85">
         <v>55</v>
@@ -6120,7 +6120,7 @@
         <v>330</v>
       </c>
       <c r="C86">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D86">
         <v>125</v>
@@ -6176,7 +6176,7 @@
         <v>332</v>
       </c>
       <c r="C87">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D87">
         <v>300</v>
@@ -6229,7 +6229,7 @@
         <v>330</v>
       </c>
       <c r="C88">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D88">
         <v>140</v>
@@ -6285,7 +6285,7 @@
         <v>332</v>
       </c>
       <c r="C89">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D89">
         <v>50</v>
@@ -6338,7 +6338,7 @@
         <v>332</v>
       </c>
       <c r="C90">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D90">
         <v>300</v>
@@ -6391,7 +6391,7 @@
         <v>329</v>
       </c>
       <c r="C91">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D91">
         <v>800</v>
@@ -6444,7 +6444,7 @@
         <v>330</v>
       </c>
       <c r="C92">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D92">
         <v>300</v>
@@ -6500,7 +6500,7 @@
         <v>330</v>
       </c>
       <c r="C93">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D93">
         <v>300</v>
@@ -6556,7 +6556,7 @@
         <v>330</v>
       </c>
       <c r="C94">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D94">
         <v>300</v>
@@ -6612,7 +6612,7 @@
         <v>330</v>
       </c>
       <c r="C95">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D95">
         <v>300</v>
@@ -6668,7 +6668,7 @@
         <v>333</v>
       </c>
       <c r="C96">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D96">
         <v>255</v>
@@ -6724,7 +6724,7 @@
         <v>330</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D97">
         <v>54</v>
@@ -6780,7 +6780,7 @@
         <v>332</v>
       </c>
       <c r="C98">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D98">
         <v>25</v>
@@ -6833,7 +6833,7 @@
         <v>330</v>
       </c>
       <c r="C99">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D99">
         <v>100</v>
@@ -6889,7 +6889,7 @@
         <v>332</v>
       </c>
       <c r="C100">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D100">
         <v>500</v>
@@ -6942,7 +6942,7 @@
         <v>329</v>
       </c>
       <c r="C101">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D101">
         <v>200</v>
@@ -6995,7 +6995,7 @@
         <v>329</v>
       </c>
       <c r="C102">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D102">
         <v>300</v>
@@ -7048,7 +7048,7 @@
         <v>332</v>
       </c>
       <c r="C103">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D103">
         <v>50</v>
@@ -7101,7 +7101,7 @@
         <v>332</v>
       </c>
       <c r="C104">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D104">
         <v>52.2</v>
@@ -7154,7 +7154,7 @@
         <v>332</v>
       </c>
       <c r="C105">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D105">
         <v>11</v>
@@ -7207,7 +7207,7 @@
         <v>330</v>
       </c>
       <c r="C106">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D106">
         <v>100</v>
@@ -7263,7 +7263,7 @@
         <v>330</v>
       </c>
       <c r="C107">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D107">
         <v>100</v>
@@ -7319,7 +7319,7 @@
         <v>332</v>
       </c>
       <c r="C108">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D108">
         <v>35</v>
@@ -7372,7 +7372,7 @@
         <v>332</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D109">
         <v>35</v>
@@ -7425,7 +7425,7 @@
         <v>330</v>
       </c>
       <c r="C110">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D110">
         <v>80</v>
@@ -7481,7 +7481,7 @@
         <v>330</v>
       </c>
       <c r="C111">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D111">
         <v>75</v>
@@ -7537,7 +7537,7 @@
         <v>332</v>
       </c>
       <c r="C112">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D112">
         <v>80</v>
@@ -7590,7 +7590,7 @@
         <v>330</v>
       </c>
       <c r="C113">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D113">
         <v>250</v>
@@ -7646,7 +7646,7 @@
         <v>330</v>
       </c>
       <c r="C114">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D114">
         <v>126</v>
@@ -7702,7 +7702,7 @@
         <v>329</v>
       </c>
       <c r="C115">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D115">
         <v>20</v>
@@ -7755,7 +7755,7 @@
         <v>329</v>
       </c>
       <c r="C116">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D116">
         <v>20</v>
@@ -7808,7 +7808,7 @@
         <v>330</v>
       </c>
       <c r="C117">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D117">
         <v>126</v>
@@ -7864,7 +7864,7 @@
         <v>330</v>
       </c>
       <c r="C118">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D118">
         <v>19.99</v>
@@ -7920,7 +7920,7 @@
         <v>330</v>
       </c>
       <c r="C119">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D119">
         <v>18</v>
@@ -7976,7 +7976,7 @@
         <v>330</v>
       </c>
       <c r="C120">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -8032,7 +8032,7 @@
         <v>330</v>
       </c>
       <c r="C121">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D121">
         <v>50</v>
@@ -8088,7 +8088,7 @@
         <v>330</v>
       </c>
       <c r="C122">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D122">
         <v>150</v>
@@ -8144,7 +8144,7 @@
         <v>330</v>
       </c>
       <c r="C123">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D123">
         <v>70</v>
@@ -8200,7 +8200,7 @@
         <v>330</v>
       </c>
       <c r="C124">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D124">
         <v>150</v>
@@ -8256,7 +8256,7 @@
         <v>332</v>
       </c>
       <c r="C125">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D125">
         <v>20</v>
@@ -8309,7 +8309,7 @@
         <v>332</v>
       </c>
       <c r="C126">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D126">
         <v>240</v>
@@ -8362,7 +8362,7 @@
         <v>332</v>
       </c>
       <c r="C127">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D127">
         <v>50</v>
@@ -8415,7 +8415,7 @@
         <v>332</v>
       </c>
       <c r="C128">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D128">
         <v>20</v>
@@ -8468,7 +8468,7 @@
         <v>330</v>
       </c>
       <c r="C129">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D129">
         <v>140</v>
@@ -8524,7 +8524,7 @@
         <v>332</v>
       </c>
       <c r="C130">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D130">
         <v>11</v>
@@ -8577,7 +8577,7 @@
         <v>330</v>
       </c>
       <c r="C131">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D131">
         <v>65</v>
@@ -8633,7 +8633,7 @@
         <v>332</v>
       </c>
       <c r="C132">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D132">
         <v>30</v>
@@ -8686,7 +8686,7 @@
         <v>329</v>
       </c>
       <c r="C133">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D133">
         <v>40</v>
@@ -8739,7 +8739,7 @@
         <v>330</v>
       </c>
       <c r="C134">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D134">
         <v>50</v>
@@ -8795,7 +8795,7 @@
         <v>332</v>
       </c>
       <c r="C135">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D135">
         <v>300</v>
@@ -8848,7 +8848,7 @@
         <v>332</v>
       </c>
       <c r="C136">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D136">
         <v>50</v>
@@ -8901,7 +8901,7 @@
         <v>330</v>
       </c>
       <c r="C137">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D137">
         <v>98</v>
@@ -8957,7 +8957,7 @@
         <v>330</v>
       </c>
       <c r="C138">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D138">
         <v>206.6</v>
@@ -9013,7 +9013,7 @@
         <v>330</v>
       </c>
       <c r="C139">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D139">
         <v>300</v>
@@ -9069,7 +9069,7 @@
         <v>332</v>
       </c>
       <c r="C140">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D140">
         <v>100</v>
@@ -9122,7 +9122,7 @@
         <v>330</v>
       </c>
       <c r="C141">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D141">
         <v>148</v>
@@ -9178,7 +9178,7 @@
         <v>330</v>
       </c>
       <c r="C142">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D142">
         <v>12</v>
@@ -9234,7 +9234,7 @@
         <v>329</v>
       </c>
       <c r="C143">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D143">
         <v>100</v>
@@ -9287,7 +9287,7 @@
         <v>330</v>
       </c>
       <c r="C144">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D144">
         <v>15.75</v>
@@ -9343,7 +9343,7 @@
         <v>332</v>
       </c>
       <c r="C145">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D145">
         <v>75</v>
@@ -9396,7 +9396,7 @@
         <v>330</v>
       </c>
       <c r="C146">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D146">
         <v>50</v>
@@ -9452,7 +9452,7 @@
         <v>330</v>
       </c>
       <c r="C147">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D147">
         <v>20</v>
@@ -9508,7 +9508,7 @@
         <v>330</v>
       </c>
       <c r="C148">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D148">
         <v>20</v>
@@ -9564,7 +9564,7 @@
         <v>329</v>
       </c>
       <c r="C149">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D149">
         <v>95</v>
@@ -9617,7 +9617,7 @@
         <v>330</v>
       </c>
       <c r="C150">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D150">
         <v>19.9</v>
@@ -9673,7 +9673,7 @@
         <v>330</v>
       </c>
       <c r="C151">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D151">
         <v>20</v>
@@ -9729,7 +9729,7 @@
         <v>329</v>
       </c>
       <c r="C152">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D152">
         <v>126.5</v>
@@ -9782,7 +9782,7 @@
         <v>329</v>
       </c>
       <c r="C153">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D153">
         <v>250</v>
@@ -9835,7 +9835,7 @@
         <v>329</v>
       </c>
       <c r="C154">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D154">
         <v>202.4</v>
@@ -9888,7 +9888,7 @@
         <v>332</v>
       </c>
       <c r="C155">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D155">
         <v>197.2</v>
@@ -9941,7 +9941,7 @@
         <v>330</v>
       </c>
       <c r="C156">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D156">
         <v>77</v>
@@ -9997,7 +9997,7 @@
         <v>329</v>
       </c>
       <c r="C157">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D157">
         <v>150</v>
@@ -10050,7 +10050,7 @@
         <v>329</v>
       </c>
       <c r="C158">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D158">
         <v>53.9</v>
@@ -10103,7 +10103,7 @@
         <v>329</v>
       </c>
       <c r="C159">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D159">
         <v>40</v>
@@ -10156,7 +10156,7 @@
         <v>329</v>
       </c>
       <c r="C160">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D160">
         <v>20</v>
@@ -10209,7 +10209,7 @@
         <v>329</v>
       </c>
       <c r="C161">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D161">
         <v>20</v>
@@ -10262,7 +10262,7 @@
         <v>332</v>
       </c>
       <c r="C162">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D162">
         <v>20</v>
@@ -10315,7 +10315,7 @@
         <v>330</v>
       </c>
       <c r="C163">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D163">
         <v>60</v>
@@ -10371,7 +10371,7 @@
         <v>330</v>
       </c>
       <c r="C164">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D164">
         <v>100</v>
@@ -10427,7 +10427,7 @@
         <v>330</v>
       </c>
       <c r="C165">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D165">
         <v>100</v>
@@ -10483,7 +10483,7 @@
         <v>330</v>
       </c>
       <c r="C166">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D166">
         <v>15</v>
@@ -10539,7 +10539,7 @@
         <v>330</v>
       </c>
       <c r="C167">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D167">
         <v>15</v>
@@ -10595,7 +10595,7 @@
         <v>330</v>
       </c>
       <c r="C168">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D168">
         <v>30</v>
@@ -10651,7 +10651,7 @@
         <v>330</v>
       </c>
       <c r="C169">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D169">
         <v>30</v>
@@ -10707,7 +10707,7 @@
         <v>330</v>
       </c>
       <c r="C170">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D170">
         <v>174.8</v>
@@ -10763,7 +10763,7 @@
         <v>330</v>
       </c>
       <c r="C171">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D171">
         <v>50</v>
@@ -10819,7 +10819,7 @@
         <v>330</v>
       </c>
       <c r="C172">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D172">
         <v>60</v>
@@ -10875,7 +10875,7 @@
         <v>332</v>
       </c>
       <c r="C173">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D173">
         <v>100</v>
@@ -10928,7 +10928,7 @@
         <v>330</v>
       </c>
       <c r="C174">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D174">
         <v>80</v>
@@ -10984,7 +10984,7 @@
         <v>330</v>
       </c>
       <c r="C175">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D175">
         <v>20</v>
@@ -11040,7 +11040,7 @@
         <v>330</v>
       </c>
       <c r="C176">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D176">
         <v>55</v>
@@ -11096,7 +11096,7 @@
         <v>330</v>
       </c>
       <c r="C177">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D177">
         <v>20</v>
@@ -11152,7 +11152,7 @@
         <v>330</v>
       </c>
       <c r="C178">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D178">
         <v>20</v>
@@ -11208,7 +11208,7 @@
         <v>330</v>
       </c>
       <c r="C179">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D179">
         <v>41</v>
@@ -11264,7 +11264,7 @@
         <v>330</v>
       </c>
       <c r="C180">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D180">
         <v>25</v>
@@ -11320,7 +11320,7 @@
         <v>330</v>
       </c>
       <c r="C181">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D181">
         <v>65</v>
@@ -11376,7 +11376,7 @@
         <v>332</v>
       </c>
       <c r="C182">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D182">
         <v>50</v>
@@ -11429,7 +11429,7 @@
         <v>332</v>
       </c>
       <c r="C183">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D183">
         <v>75</v>
@@ -11482,7 +11482,7 @@
         <v>329</v>
       </c>
       <c r="C184">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D184">
         <v>150</v>
@@ -11535,7 +11535,7 @@
         <v>329</v>
       </c>
       <c r="C185">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D185">
         <v>150</v>
@@ -11588,7 +11588,7 @@
         <v>330</v>
       </c>
       <c r="C186">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D186">
         <v>200</v>
@@ -11644,7 +11644,7 @@
         <v>332</v>
       </c>
       <c r="C187">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D187">
         <v>50</v>
@@ -11697,7 +11697,7 @@
         <v>330</v>
       </c>
       <c r="C188">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D188">
         <v>46.8</v>
@@ -11753,7 +11753,7 @@
         <v>330</v>
       </c>
       <c r="C189">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D189">
         <v>150</v>
@@ -11809,7 +11809,7 @@
         <v>330</v>
       </c>
       <c r="C190">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D190">
         <v>150</v>
@@ -11865,7 +11865,7 @@
         <v>332</v>
       </c>
       <c r="C191">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D191">
         <v>75</v>
@@ -11918,7 +11918,7 @@
         <v>332</v>
       </c>
       <c r="C192">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D192">
         <v>20</v>
@@ -11971,7 +11971,7 @@
         <v>330</v>
       </c>
       <c r="C193">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D193">
         <v>200</v>
@@ -12027,7 +12027,7 @@
         <v>332</v>
       </c>
       <c r="C194">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D194">
         <v>11</v>
@@ -12080,7 +12080,7 @@
         <v>332</v>
       </c>
       <c r="C195">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D195">
         <v>11</v>
@@ -12133,7 +12133,7 @@
         <v>330</v>
       </c>
       <c r="C196">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D196">
         <v>127</v>
@@ -12189,7 +12189,7 @@
         <v>330</v>
       </c>
       <c r="C197">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D197">
         <v>53</v>
@@ -12245,7 +12245,7 @@
         <v>330</v>
       </c>
       <c r="C198">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D198">
         <v>60</v>
@@ -12301,7 +12301,7 @@
         <v>334</v>
       </c>
       <c r="C199">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D199">
         <v>569</v>
@@ -12357,7 +12357,7 @@
         <v>332</v>
       </c>
       <c r="C200">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D200">
         <v>75</v>
@@ -12410,7 +12410,7 @@
         <v>332</v>
       </c>
       <c r="C201">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D201">
         <v>122</v>
@@ -12463,7 +12463,7 @@
         <v>330</v>
       </c>
       <c r="C202">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D202">
         <v>314</v>
@@ -12519,7 +12519,7 @@
         <v>332</v>
       </c>
       <c r="C203">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D203">
         <v>74.5</v>
@@ -12572,7 +12572,7 @@
         <v>330</v>
       </c>
       <c r="C204">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D204">
         <v>20</v>
@@ -12628,7 +12628,7 @@
         <v>330</v>
       </c>
       <c r="C205">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D205">
         <v>70</v>
@@ -12684,7 +12684,7 @@
         <v>329</v>
       </c>
       <c r="C206">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D206">
         <v>127.86</v>
@@ -12737,7 +12737,7 @@
         <v>329</v>
       </c>
       <c r="C207">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D207">
         <v>130</v>
@@ -12790,7 +12790,7 @@
         <v>332</v>
       </c>
       <c r="C208">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D208">
         <v>11</v>
@@ -12843,7 +12843,7 @@
         <v>329</v>
       </c>
       <c r="C209">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D209">
         <v>150</v>
@@ -12896,7 +12896,7 @@
         <v>330</v>
       </c>
       <c r="C210">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D210">
         <v>82.5</v>
@@ -12952,7 +12952,7 @@
         <v>330</v>
       </c>
       <c r="C211">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D211">
         <v>18</v>
@@ -13008,7 +13008,7 @@
         <v>332</v>
       </c>
       <c r="C212">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D212">
         <v>75</v>
@@ -13061,7 +13061,7 @@
         <v>330</v>
       </c>
       <c r="C213">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D213">
         <v>150</v>
@@ -13117,7 +13117,7 @@
         <v>330</v>
       </c>
       <c r="C214">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D214">
         <v>90</v>
@@ -13173,7 +13173,7 @@
         <v>330</v>
       </c>
       <c r="C215">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D215">
         <v>36</v>
@@ -13229,7 +13229,7 @@
         <v>330</v>
       </c>
       <c r="C216">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D216">
         <v>80</v>
@@ -13285,7 +13285,7 @@
         <v>330</v>
       </c>
       <c r="C217">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D217">
         <v>500</v>
@@ -13341,7 +13341,7 @@
         <v>330</v>
       </c>
       <c r="C218">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D218">
         <v>72</v>
@@ -13397,7 +13397,7 @@
         <v>330</v>
       </c>
       <c r="C219">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D219">
         <v>54</v>
@@ -13453,7 +13453,7 @@
         <v>332</v>
       </c>
       <c r="C220">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D220">
         <v>100</v>
@@ -13506,7 +13506,7 @@
         <v>330</v>
       </c>
       <c r="C221">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D221">
         <v>100</v>
@@ -13562,7 +13562,7 @@
         <v>330</v>
       </c>
       <c r="C222">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D222">
         <v>30</v>
@@ -13618,7 +13618,7 @@
         <v>330</v>
       </c>
       <c r="C223">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D223">
         <v>70</v>
@@ -13674,7 +13674,7 @@
         <v>330</v>
       </c>
       <c r="C224">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D224">
         <v>63</v>
@@ -13730,7 +13730,7 @@
         <v>330</v>
       </c>
       <c r="C225">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D225">
         <v>94</v>
@@ -13786,7 +13786,7 @@
         <v>330</v>
       </c>
       <c r="C226">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D226">
         <v>150</v>
@@ -13842,7 +13842,7 @@
         <v>330</v>
       </c>
       <c r="C227">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D227">
         <v>117</v>
@@ -13898,7 +13898,7 @@
         <v>332</v>
       </c>
       <c r="C228">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D228">
         <v>20</v>
@@ -13951,7 +13951,7 @@
         <v>330</v>
       </c>
       <c r="C229">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D229">
         <v>90</v>
@@ -14007,7 +14007,7 @@
         <v>330</v>
       </c>
       <c r="C230">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D230">
         <v>107</v>
@@ -14063,7 +14063,7 @@
         <v>330</v>
       </c>
       <c r="C231">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D231">
         <v>118.56</v>
@@ -14119,7 +14119,7 @@
         <v>330</v>
       </c>
       <c r="C232">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D232">
         <v>75</v>
@@ -14175,7 +14175,7 @@
         <v>330</v>
       </c>
       <c r="C233">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D233">
         <v>75</v>
@@ -14231,7 +14231,7 @@
         <v>332</v>
       </c>
       <c r="C234">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D234">
         <v>26</v>
@@ -14284,7 +14284,7 @@
         <v>332</v>
       </c>
       <c r="C235">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D235">
         <v>26</v>
@@ -14337,7 +14337,7 @@
         <v>330</v>
       </c>
       <c r="C236">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D236">
         <v>90</v>
@@ -14393,7 +14393,7 @@
         <v>330</v>
       </c>
       <c r="C237">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D237">
         <v>150</v>
@@ -14449,7 +14449,7 @@
         <v>330</v>
       </c>
       <c r="C238">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D238">
         <v>20</v>
@@ -14505,7 +14505,7 @@
         <v>330</v>
       </c>
       <c r="C239">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D239">
         <v>15</v>
@@ -14561,7 +14561,7 @@
         <v>330</v>
       </c>
       <c r="C240">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D240">
         <v>15</v>
@@ -14617,7 +14617,7 @@
         <v>330</v>
       </c>
       <c r="C241">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D241">
         <v>15</v>
@@ -14673,7 +14673,7 @@
         <v>330</v>
       </c>
       <c r="C242">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D242">
         <v>10</v>
@@ -14729,7 +14729,7 @@
         <v>330</v>
       </c>
       <c r="C243">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D243">
         <v>150</v>
@@ -14785,7 +14785,7 @@
         <v>332</v>
       </c>
       <c r="C244">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D244">
         <v>11</v>
@@ -14838,7 +14838,7 @@
         <v>329</v>
       </c>
       <c r="C245">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D245">
         <v>80</v>
@@ -14891,7 +14891,7 @@
         <v>329</v>
       </c>
       <c r="C246">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D246">
         <v>20</v>
@@ -14944,7 +14944,7 @@
         <v>330</v>
       </c>
       <c r="C247">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D247">
         <v>60</v>
@@ -15000,7 +15000,7 @@
         <v>330</v>
       </c>
       <c r="C248">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D248">
         <v>102</v>
@@ -15056,7 +15056,7 @@
         <v>332</v>
       </c>
       <c r="C249">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D249">
         <v>75</v>
@@ -15109,7 +15109,7 @@
         <v>329</v>
       </c>
       <c r="C250">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D250">
         <v>50</v>
@@ -15162,7 +15162,7 @@
         <v>330</v>
       </c>
       <c r="C251">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D251">
         <v>150</v>
@@ -15218,7 +15218,7 @@
         <v>332</v>
       </c>
       <c r="C252">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D252">
         <v>75</v>
@@ -15271,7 +15271,7 @@
         <v>330</v>
       </c>
       <c r="C253">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D253">
         <v>62</v>
@@ -15327,7 +15327,7 @@
         <v>330</v>
       </c>
       <c r="C254">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D254">
         <v>60</v>
@@ -15383,7 +15383,7 @@
         <v>332</v>
       </c>
       <c r="C255">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D255">
         <v>100</v>
@@ -15436,7 +15436,7 @@
         <v>332</v>
       </c>
       <c r="C256">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D256">
         <v>100</v>
@@ -15489,7 +15489,7 @@
         <v>330</v>
       </c>
       <c r="C257">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D257">
         <v>20</v>
@@ -15545,7 +15545,7 @@
         <v>329</v>
       </c>
       <c r="C258">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D258">
         <v>62.5</v>
@@ -15598,7 +15598,7 @@
         <v>330</v>
       </c>
       <c r="C259">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D259">
         <v>14.2</v>
@@ -15654,7 +15654,7 @@
         <v>330</v>
       </c>
       <c r="C260">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D260">
         <v>128</v>
@@ -15710,7 +15710,7 @@
         <v>332</v>
       </c>
       <c r="C261">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D261">
         <v>160</v>
@@ -15763,7 +15763,7 @@
         <v>330</v>
       </c>
       <c r="C262">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D262">
         <v>20</v>
@@ -15819,7 +15819,7 @@
         <v>330</v>
       </c>
       <c r="C263">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D263">
         <v>150</v>
@@ -15875,7 +15875,7 @@
         <v>329</v>
       </c>
       <c r="C264">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D264">
         <v>150</v>
@@ -15928,7 +15928,7 @@
         <v>330</v>
       </c>
       <c r="C265">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D265">
         <v>500</v>
@@ -15984,7 +15984,7 @@
         <v>330</v>
       </c>
       <c r="C266">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D266">
         <v>50</v>
@@ -16040,7 +16040,7 @@
         <v>332</v>
       </c>
       <c r="C267">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D267">
         <v>11</v>
@@ -16093,7 +16093,7 @@
         <v>332</v>
       </c>
       <c r="C268">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D268">
         <v>11</v>
@@ -16146,7 +16146,7 @@
         <v>332</v>
       </c>
       <c r="C269">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D269">
         <v>127.5</v>
@@ -16199,7 +16199,7 @@
         <v>332</v>
       </c>
       <c r="C270">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D270">
         <v>100</v>
@@ -16252,7 +16252,7 @@
         <v>332</v>
       </c>
       <c r="C271">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D271">
         <v>100</v>
@@ -16305,7 +16305,7 @@
         <v>331</v>
       </c>
       <c r="C272">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D272">
         <v>833</v>
@@ -16361,7 +16361,7 @@
         <v>331</v>
       </c>
       <c r="C273">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D273">
         <v>836</v>
@@ -16417,7 +16417,7 @@
         <v>331</v>
       </c>
       <c r="C274">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D274">
         <v>820</v>
@@ -16473,7 +16473,7 @@
         <v>331</v>
       </c>
       <c r="C275">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D275">
         <v>800.1</v>
@@ -16529,7 +16529,7 @@
         <v>331</v>
       </c>
       <c r="C276">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D276">
         <v>800.1</v>
@@ -16585,7 +16585,7 @@
         <v>329</v>
       </c>
       <c r="C277">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D277">
         <v>75</v>
@@ -16638,7 +16638,7 @@
         <v>329</v>
       </c>
       <c r="C278">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D278">
         <v>79</v>
@@ -16691,7 +16691,7 @@
         <v>330</v>
       </c>
       <c r="C279">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D279">
         <v>260</v>
@@ -16747,7 +16747,7 @@
         <v>330</v>
       </c>
       <c r="C280">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D280">
         <v>90</v>
@@ -16803,7 +16803,7 @@
         <v>330</v>
       </c>
       <c r="C281">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D281">
         <v>250</v>
@@ -16859,7 +16859,7 @@
         <v>330</v>
       </c>
       <c r="C282">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D282">
         <v>167</v>
@@ -16915,7 +16915,7 @@
         <v>329</v>
       </c>
       <c r="C283">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D283">
         <v>20</v>
@@ -16968,7 +16968,7 @@
         <v>329</v>
       </c>
       <c r="C284">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D284">
         <v>20</v>
@@ -17021,7 +17021,7 @@
         <v>329</v>
       </c>
       <c r="C285">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D285">
         <v>20</v>
@@ -17074,7 +17074,7 @@
         <v>330</v>
       </c>
       <c r="C286">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D286">
         <v>125</v>
@@ -17130,7 +17130,7 @@
         <v>332</v>
       </c>
       <c r="C287">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D287">
         <v>11</v>
@@ -17183,7 +17183,7 @@
         <v>330</v>
       </c>
       <c r="C288">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D288">
         <v>150</v>
@@ -17239,7 +17239,7 @@
         <v>329</v>
       </c>
       <c r="C289">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D289">
         <v>20</v>
@@ -17292,7 +17292,7 @@
         <v>330</v>
       </c>
       <c r="C290">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D290">
         <v>80</v>
@@ -17348,7 +17348,7 @@
         <v>330</v>
       </c>
       <c r="C291">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D291">
         <v>188.5</v>
@@ -17404,7 +17404,7 @@
         <v>330</v>
       </c>
       <c r="C292">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D292">
         <v>45</v>
@@ -17460,7 +17460,7 @@
         <v>330</v>
       </c>
       <c r="C293">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D293">
         <v>55</v>
@@ -17516,7 +17516,7 @@
         <v>332</v>
       </c>
       <c r="C294">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D294">
         <v>50</v>
@@ -17569,7 +17569,7 @@
         <v>332</v>
       </c>
       <c r="C295">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D295">
         <v>200</v>
@@ -17622,7 +17622,7 @@
         <v>329</v>
       </c>
       <c r="C296">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D296">
         <v>106</v>
@@ -17675,7 +17675,7 @@
         <v>330</v>
       </c>
       <c r="C297">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D297">
         <v>65</v>
@@ -17731,7 +17731,7 @@
         <v>330</v>
       </c>
       <c r="C298">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D298">
         <v>90</v>
@@ -17787,7 +17787,7 @@
         <v>330</v>
       </c>
       <c r="C299">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D299">
         <v>100</v>
@@ -17843,7 +17843,7 @@
         <v>330</v>
       </c>
       <c r="C300">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D300">
         <v>250</v>
@@ -17899,7 +17899,7 @@
         <v>330</v>
       </c>
       <c r="C301">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D301">
         <v>225</v>
@@ -17955,7 +17955,7 @@
         <v>330</v>
       </c>
       <c r="C302">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D302">
         <v>222</v>
@@ -18011,7 +18011,7 @@
         <v>330</v>
       </c>
       <c r="C303">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D303">
         <v>150</v>
@@ -18067,7 +18067,7 @@
         <v>330</v>
       </c>
       <c r="C304">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D304">
         <v>50</v>
@@ -18123,7 +18123,7 @@
         <v>329</v>
       </c>
       <c r="C305">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D305">
         <v>120</v>
@@ -18176,7 +18176,7 @@
         <v>330</v>
       </c>
       <c r="C306">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D306">
         <v>82</v>
@@ -18232,7 +18232,7 @@
         <v>330</v>
       </c>
       <c r="C307">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D307">
         <v>70</v>
@@ -18288,7 +18288,7 @@
         <v>330</v>
       </c>
       <c r="C308">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D308">
         <v>57</v>
@@ -18344,7 +18344,7 @@
         <v>332</v>
       </c>
       <c r="C309">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D309">
         <v>22</v>
@@ -18397,7 +18397,7 @@
         <v>330</v>
       </c>
       <c r="C310">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D310">
         <v>98</v>
@@ -18453,7 +18453,7 @@
         <v>330</v>
       </c>
       <c r="C311">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D311">
         <v>64.2</v>
@@ -18509,7 +18509,7 @@
         <v>330</v>
       </c>
       <c r="C312">
-        <v>5</v>
+        <v>0.001</v>
       </c>
       <c r="D312">
         <v>120</v>

--- a/Thesis/developer_states_exported.xlsx
+++ b/Thesis/developer_states_exported.xlsx
@@ -1841,9 +1841,6 @@
       <c r="G8" t="s">
         <v>350</v>
       </c>
-      <c r="I8">
-        <v>40783.17</v>
-      </c>
       <c r="J8">
         <v>2000.5</v>
       </c>
@@ -16723,6 +16720,9 @@
       <c r="G279" t="s">
         <v>350</v>
       </c>
+      <c r="H279">
+        <v>99.92644024483629</v>
+      </c>
       <c r="J279">
         <v>1483</v>
       </c>
@@ -16890,6 +16890,9 @@
       </c>
       <c r="G282" t="s">
         <v>350</v>
+      </c>
+      <c r="H282">
+        <v>0.07317073170731707</v>
       </c>
       <c r="J282">
         <v>1483</v>
